--- a/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Papa dit : fini. L'adulte dit fini. Sami écoute. Il va éteindre. Sami éteint l'écran. L'écran devient noir. Il pose la tablette. Papa dit : on prend un autre jeu. Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute. Sami dit : l'écran est éteint. Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment, maman dit : fini. L'adulte dit fini. Sami se souvient. Il éteint. Il pose la télécommande. Maman dit : un autre jeu. Sami prend le ballon souple. Ils se le passent. Maman dit : tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint. Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
+          <t>Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Fini. L'adulte dit fini. Sami écoute. Il va éteindre. Sami éteint l'écran. L'écran devient noir. Il pose la tablette. On prend un autre jeu. Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute. L'écran est éteint. Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment, Fini. L'adulte dit fini. Sami se souvient. Il éteint. Il pose la télécommande. Un autre jeu. Sami prend le ballon souple. Ils se le passent. Tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint. Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,23 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui.
+papa|Fini. L'adulte dit fini.
+narrateur|Sami écoute. Il va éteindre. Sami éteint l'écran. L'écran devient noir. Il pose la tablette.
+papa|On prend un autre jeu.
+narrateur|Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute.
+enfant-m|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment,
+maman|Fini. L'adulte dit fini.
+narrateur|Sami se souvient. Il éteint. Il pose la télécommande.
+maman|Un autre jeu.
+narrateur|Sami prend le ballon souple. Ils se le passent.
+maman|Tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint.
+narrateur|Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Sami ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a dit fini. Sami a éteint. Il a pris un autre jeu. Plus tard, avec maman, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range le ballon. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1322,6 +1327,7 @@
 narrateur|Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Papa dit fini. Que fait Sami ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Papa a dit fini. Sami a éteint. Il a pris un autre jeu. Plus tard, avec maman, pareil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Sami range le ballon. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sami éteint, puis choisit un jeu</t>
+          <t>La pluie et les deux jeux</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie dessine des chemins sur la vitre. Papa dit fini. Raphaël éteint la tablette. Il prend les cubes. Plus tard, maman dit fini. Il prend le ballon.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Fini. L'adulte dit fini. Sami écoute. Il va éteindre. Sami éteint l'écran. L'écran devient noir. Il pose la tablette. On prend un autre jeu. Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute. L'écran est éteint. Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment, Fini. L'adulte dit fini. Sami se souvient. Il éteint. Il pose la télécommande. Un autre jeu. Sami prend le ballon souple. Ils se le passent. Tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint. Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
+          <t>La pluie dessine des chemins sur la vitre. Le rebord de la fenêtre est mouillé. Dans le salon, c'est doux. Ça sent le pain du goûter. Raphaël vit ici, avec papa et maman. Le tapis est épais, couleur sable. En ce moment, Raphaël regarde un dessin. Le dessin est sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Raphaël. Fini. Raphaël écoute. Il éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Ils construisent une tour. La tour est haute. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Plus tard, la pluie tombe encore. Maman allume un dessin à la télé. Les couleurs bougent sur le mur. Après un moment, maman s'assoit. Raphaël. Fini. Raphaël se souvient. Il éteint. Il pose la télécommande. Bravo, Raphaël. Tu as éteint. Un autre jeu. Le ballon souple. Ils se le passent, tout doucement. Le ballon est un peu lourd. Tu as repris le geste. Même leçon, autre écran. Quand on dit fini, on éteint. Puis on prend un autre jeu. C'est du bon travail. Merci, maman. Merci, papa. Raphaël rit. Le salon est calme. La pluie chante encore, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,22 +1325,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui.
-papa|Fini. L'adulte dit fini.
-narrateur|Sami écoute. Il va éteindre. Sami éteint l'écran. L'écran devient noir. Il pose la tablette.
+          <t>narrateur|La pluie dessine des chemins sur la vitre.
+narrateur|Le rebord de la fenêtre est mouillé.
+narrateur|Dans le salon, c'est doux.
+narrateur|Ça sent le pain du goûter.
+narrateur|Raphaël vit ici, avec papa et maman.
+narrateur|Le tapis est épais, couleur sable.
+narrateur|En ce moment, Raphaël regarde un dessin.
+narrateur|Le dessin est sur la tablette.
+narrateur|Les couleurs dansent.
+narrateur|Papa s'assoit près de lui.
+papa|Raphaël.
+papa|Fini.
+narrateur|Raphaël écoute.
+narrateur|Il éteint l'écran.
+narrateur|L'écran devient noir.
+narrateur|Il pose la tablette.
+papa|Bravo, Raphaël.
+papa|Tu as éteint.
 papa|On prend un autre jeu.
-narrateur|Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute.
+papa|Tu vas choisir ?
+enfant-m|Les cubes en bois.
+narrateur|Ils construisent une tour.
+narrateur|La tour est haute.
 enfant-m|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment,
-maman|Fini. L'adulte dit fini.
-narrateur|Sami se souvient. Il éteint. Il pose la télécommande.
+papa|Oui.
+papa|Un autre jeu, c'est bien.
+papa|Bravo.
+narrateur|Plus tard, la pluie tombe encore.
+narrateur|Maman allume un dessin à la télé.
+narrateur|Les couleurs bougent sur le mur.
+narrateur|Après un moment, maman s'assoit.
+maman|Raphaël.
+maman|Fini.
+narrateur|Raphaël se souvient.
+narrateur|Il éteint.
+narrateur|Il pose la télécommande.
+maman|Bravo, Raphaël.
+maman|Tu as éteint.
 maman|Un autre jeu.
-narrateur|Sami prend le ballon souple. Ils se le passent.
-maman|Tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint.
-narrateur|Puis on prend un autre jeu. Sami rit. Le salon est calme.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Le ballon souple.
+narrateur|Ils se le passent, tout doucement.
+narrateur|Le ballon est un peu lourd.
+maman|Tu as repris le geste.
+maman|Même leçon, autre écran.
+maman|Quand on dit fini, on éteint.
+maman|Puis on prend un autre jeu.
+papa|C'est du bon travail.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+narrateur|Raphaël rit.
+narrateur|Le salon est calme.
+narrateur|La pluie chante encore, dehors.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,ballon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1352,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa dit fini. Que fait Sami ?</t>
+          <t>Papa dit fini. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1564,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa dit fini. Que fait Sami ?</t>
+          <t>narrateur|Papa dit fini.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. Sami a éteint. Il a pris un autre jeu. Plus tard, avec maman, pareil.</t>
+          <t>Papa a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint la tablette ? Oui, papa. J'ai pris les cubes. Plus tard, avec moi, pareil. Tu as éteint la télé. Oui. J'ai pris le ballon. Bravo, Raphaël. Quand on dit fini, on éteint. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1737,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Papa a dit fini. Sami a éteint. Il a pris un autre jeu. Plus tard, avec maman, pareil.</t>
+          <t>narrateur|Papa a dit fini.
+narrateur|Raphaël a éteint.
+narrateur|Il a pris un autre jeu.
+papa|Tu as éteint la tablette ?
+enfant-m|Oui, papa.
+enfant-m|J'ai pris les cubes.
+maman|Plus tard, avec moi, pareil.
+maman|Tu as éteint la télé.
+enfant-m|Oui.
+enfant-m|J'ai pris le ballon.
+papa|Bravo, Raphaël.
+maman|Quand on dit fini, on éteint.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sami range le ballon. Papa et maman sont là.</t>
+          <t>Raphaël range le ballon. Le ballon rentre dans le panier. Tu as rangé ? Oui, papa. Le salon est calme. La pluie chante encore. On reste encore un peu ensemble ? Oui. Merci, papa. Merci, maman. Merci, Raphaël. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1913,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sami range le ballon. Papa et maman sont là.</t>
+          <t>narrateur|Raphaël range le ballon.
+narrateur|Le ballon rentre dans le panier.
+papa|Tu as rangé ?
+enfant-m|Oui, papa.
+maman|Le salon est calme.
+maman|La pluie chante encore.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Merci, Raphaël.
+papa|Tu as éteint.
+papa|Tu as choisi un autre jeu.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa a dit fini. J'ai éteint. On a joué aux cubes. Puis au ballon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Papa a dit fini.
+enfant-m|J'ai éteint.
+enfant-m|On a joué aux cubes.
+enfant-m|Puis au ballon.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie dessine des chemins sur la vitre. Le rebord de la fenêtre est mouillé. Dans le salon, c'est doux. Ça sent le pain du goûter. Raphaël vit ici, avec papa et maman. Le tapis est épais, couleur sable. En ce moment, Raphaël regarde un dessin. Le dessin est sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Raphaël. Fini. Raphaël écoute. Il éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Ils construisent une tour. La tour est haute. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Plus tard, la pluie tombe encore. Maman allume un dessin à la télé. Les couleurs bougent sur le mur. Après un moment, maman s'assoit. Raphaël. Fini. Raphaël se souvient. Il éteint. Il pose la télécommande. Bravo, Raphaël. Tu as éteint. Un autre jeu. Le ballon souple. Ils se le passent, tout doucement. Le ballon est un peu lourd. Tu as repris le geste. Même leçon, autre écran. Quand on dit fini, on éteint. Puis on prend un autre jeu. C'est du bon travail. Merci, maman. Merci, papa. Raphaël rit. Le salon est calme. La pluie chante encore, dehors.</t>
+          <t>La pluie dessine des chemins sur la vitre. Le rebord de la fenêtre est mouillé. Dans le salon, c'est doux. Ça sent le pain du goûter. Raphaël vit ici, avec papa et maman. Le tapis est épais, couleur sable. Là, sur ses genoux, la tablette est allumée. Raphaël regarde un dessin. Les couleurs dansent. La pluie tape la gouttière. Papa s'assoit près de lui. Raphaël. Fini. Raphaël écoute. Il éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Ils construisent une tour. Le bois sent la forêt. La tour est haute. Tu as entendu la gouttière ? Elle fait tic tic. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Plus tard, la pluie tombe encore. Maman allume un dessin à la télé. Les couleurs bougent sur le mur. Après un moment, maman s'assoit. Raphaël. Fini. Raphaël se souvient. Il éteint. Il pose la télécommande. Bravo, Raphaël. Tu as éteint. Un autre jeu. Le ballon souple. Ils se le passent, tout doucement. Le ballon est un peu lourd. Tu as éteint, encore. Avec la tablette, et avec la télé. Quand on dit fini, on éteint. Puis on prend un autre jeu. Merci, maman. Merci, papa. Raphaël rit. Le salon est calme. La pluie chante encore, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami est dans le salon. Il regarde un dessin sur la tablette. Les couleurs dansent. Papa s'assoit près de lui. Papa dit : fini. L'adulte dit fini. Sami écoute. Il va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Sami éteint l'écran. L'écran devient noir. Il pose la tablette. Papa dit : on prend un autre jeu. Sami va choisir un jeu. Il choisit les cubes en bois. Ils construisent une tour. La tour est haute. Sami dit : l'écran est éteint. Un autre jeu, c'est bien. Plus tard, maman allume un dessin à la télé. Après un moment, maman dit : fini. L'adulte dit fini. Sami se souvient. Il éteint. Il pose la télécommande. Maman dit : un autre jeu. Sami prend le ballon souple. Ils se le passent. Maman dit : tu as repris le geste. Même leçon, autre écran. Quand l'adulte dit fini, on éteint. Puis on prend un autre jeu. Sami rit. Le salon est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie dessine des chemins sur la vitre. Le rebord de la fenêtre est mouillé. Dans le salon, c'est doux. Ça sent le pain du goûter. Raphaël vit ici, avec papa et maman. Le tapis est épais, couleur sable. Là, sur ses genoux, la tablette est allumée. Raphaël regarde un dessin. Les couleurs dansent. La pluie tape la gouttière. Papa s'assoit près de lui. Raphaël. Fini. Raphaël écoute. Il éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Les cubes en bois. Ils construisent une tour. Le bois sent la forêt. La tour est haute. Tu as entendu la gouttière ? Elle fait tic tic. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Plus tard, la pluie tombe encore. Maman allume un dessin à la télé. Les couleurs bougent sur le mur. Après un moment, maman s'assoit. Raphaël. Fini. Raphaël se souvient. Il éteint. Il pose la télécommande. Bravo, Raphaël. Tu as éteint. Un autre jeu. Le ballon souple. Ils se le passent, tout doucement. Le ballon est un peu lourd. Tu as éteint, encore. Avec la tablette, et avec la télé. Quand on dit fini, on éteint. Puis on prend un autre jeu. Merci, maman. Merci, papa. Raphaël rit. Le salon est calme. La pluie chante encore, dehors.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1331,9 +1331,10 @@
 narrateur|Ça sent le pain du goûter.
 narrateur|Raphaël vit ici, avec papa et maman.
 narrateur|Le tapis est épais, couleur sable.
-narrateur|En ce moment, Raphaël regarde un dessin.
-narrateur|Le dessin est sur la tablette.
+narrateur|Là, sur ses genoux, la tablette est allumée.
+narrateur|Raphaël regarde un dessin.
 narrateur|Les couleurs dansent.
+narrateur|La pluie tape la gouttière.
 narrateur|Papa s'assoit près de lui.
 papa|Raphaël.
 papa|Fini.
@@ -1347,7 +1348,10 @@
 papa|Tu vas choisir ?
 enfant-m|Les cubes en bois.
 narrateur|Ils construisent une tour.
+narrateur|Le bois sent la forêt.
 narrateur|La tour est haute.
+papa|Tu as entendu la gouttière ?
+enfant-m|Elle fait tic tic.
 enfant-m|L'écran est éteint.
 papa|Oui.
 papa|Un autre jeu, c'est bien.
@@ -1367,11 +1371,10 @@
 enfant-m|Le ballon souple.
 narrateur|Ils se le passent, tout doucement.
 narrateur|Le ballon est un peu lourd.
-maman|Tu as repris le geste.
-maman|Même leçon, autre écran.
+maman|Tu as éteint, encore.
+maman|Avec la tablette, et avec la télé.
 maman|Quand on dit fini, on éteint.
 maman|Puis on prend un autre jeu.
-papa|C'est du bon travail.
 enfant-m|Merci, maman.
 enfant-m|Merci, papa.
 narrateur|Raphaël rit.
@@ -1413,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa dit fini. Que fait Sami ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa dit fini. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1571,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint la tablette ? Oui, papa. J'ai pris les cubes. Plus tard, avec moi, pareil. Tu as éteint la télé. Oui. J'ai pris le ballon. Bravo, Raphaël. Quand on dit fini, on éteint. C'est du bon travail.</t>
+          <t>Papa a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint la tablette ? Oui, papa. J'ai pris les cubes. Plus tard, avec moi, pareil. Tu as éteint la télé. Oui. J'ai pris le ballon. Bravo, Raphaël. Quand on dit fini, on éteint.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a dit fini. Sami a éteint. Il a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Plus tard, avec maman, pareil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint la tablette ? Oui, papa. J'ai pris les cubes. Plus tard, avec moi, pareil. Tu as éteint la télé. Oui. J'ai pris le ballon. Bravo, Raphaël. Quand on dit fini, on éteint.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,11 +1750,9 @@
 enfant-m|Oui.
 enfant-m|J'ai pris le ballon.
 papa|Bravo, Raphaël.
-maman|Quand on dit fini, on éteint.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Quand on dit fini, on éteint.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël range le ballon. Le ballon rentre dans le panier. Tu as rangé ? Oui, papa. Le salon est calme. La pluie chante encore. On reste encore un peu ensemble ? Oui. Merci, papa. Merci, maman. Merci, Raphaël. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
+          <t>Raphaël range le ballon. Le ballon rentre dans le panier. Tu as rangé ? Oui, papa. Le salon est calme. La pluie chante encore. On reste encore un peu ensemble ? Oui. Merci, papa. Merci, maman. Merci, Raphaël. Le ballon est rangé. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami range le ballon. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël range le ballon. Le ballon rentre dans le panier. Tu as rangé ? Oui, papa. Le salon est calme. La pluie chante encore. On reste encore un peu ensemble ? Oui. Merci, papa. Merci, maman. Merci, Raphaël. Le ballon est rangé. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,12 +1924,10 @@
 enfant-m|Merci, papa.
 enfant-m|Merci, maman.
 maman|Merci, Raphaël.
-papa|Tu as éteint.
-papa|Tu as choisi un autre jeu.
+papa|Le ballon est rangé.
 maman|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1954,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. J'ai éteint. On a joué aux cubes. Puis au ballon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Papa a dit fini. J'ai éteint. On a joué aux cubes. Puis au ballon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a dit fini. J'ai éteint. On a joué aux cubes. Puis au ballon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,12 +2096,9 @@
 enfant-m|J'ai éteint.
 enfant-m|On a joué aux cubes.
 enfant-m|Puis au ballon.
-maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-02.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
